--- a/output/2026-09-30_23_Malesia_Kedah_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-30_23_Malesia_Kedah_Depolverazione_Trattamento_aria.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,6 @@
           <t>Agro-Industrial Supplies (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Kedah</t>
